--- a/excel/Crowdpear.xlsx
+++ b/excel/Crowdpear.xlsx
@@ -1,45 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Crowdpear\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-v2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D927B9-9110-4442-91C6-E24D9AA95A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34883093-1794-4D37-985D-5F9AA8E5449C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="19" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="12" r:id="rId2"/>
-    <sheet name="Vakaro 3A K1 III" sheetId="27" r:id="rId3"/>
-    <sheet name="Kauno 36-118 II" sheetId="26" r:id="rId4"/>
-    <sheet name="Tautvilo kotedžai XIV" sheetId="24" r:id="rId5"/>
-    <sheet name="Horizonto 2A XII" sheetId="25" r:id="rId6"/>
-    <sheet name="Žemoji 52 XXIX“" sheetId="23" r:id="rId7"/>
-    <sheet name="Namas Panevėžyje" sheetId="22" r:id="rId8"/>
-    <sheet name="Vanagupės 36A-204 II" sheetId="21" r:id="rId9"/>
-    <sheet name="Vingio namai XIV" sheetId="20" r:id="rId10"/>
-    <sheet name="Druskonio perlai VII" sheetId="19" r:id="rId11"/>
-    <sheet name="Birelių namas II" sheetId="18" r:id="rId12"/>
-    <sheet name="Sūduvos 8-2" sheetId="17" r:id="rId13"/>
-    <sheet name="Miškininkų 30 II" sheetId="16" r:id="rId14"/>
-    <sheet name="Pagojo 1 II" sheetId="15" r:id="rId15"/>
-    <sheet name="Vienbutis Minsko 5A" sheetId="14" r:id="rId16"/>
-    <sheet name="Dvibutis Sodybų 12" sheetId="13" r:id="rId17"/>
-    <sheet name="Sfintii Arhangheli 21" sheetId="11" r:id="rId18"/>
-    <sheet name="Girinaičių 7 II" sheetId="10" r:id="rId19"/>
-    <sheet name="Girios 112 II" sheetId="9" r:id="rId20"/>
-    <sheet name="Piliarožių 10 VI" sheetId="8" r:id="rId21"/>
-    <sheet name="Girinaičių 7" sheetId="7" r:id="rId22"/>
-    <sheet name="Kauno 36-232" sheetId="6" r:id="rId23"/>
-    <sheet name="Sodziaus 7A (1)" sheetId="5" r:id="rId24"/>
-    <sheet name="Sodziaus 7A" sheetId="4" r:id="rId25"/>
-    <sheet name="Pušynas VII" sheetId="3" r:id="rId26"/>
-    <sheet name="Užnerio butai III" sheetId="2" r:id="rId27"/>
+    <sheet name="Užnerio butai XV" sheetId="28" r:id="rId3"/>
+    <sheet name="Vakaro 3A K1 III" sheetId="27" r:id="rId4"/>
+    <sheet name="Kauno 36-118 II" sheetId="26" r:id="rId5"/>
+    <sheet name="Tautvilo kotedžai XIV" sheetId="24" r:id="rId6"/>
+    <sheet name="Horizonto 2A XII" sheetId="25" r:id="rId7"/>
+    <sheet name="Žemoji 52 XXIX“" sheetId="23" r:id="rId8"/>
+    <sheet name="Namas Panevėžyje" sheetId="22" r:id="rId9"/>
+    <sheet name="Vanagupės 36A-204 II" sheetId="21" r:id="rId10"/>
+    <sheet name="Vingio namai XIV" sheetId="20" r:id="rId11"/>
+    <sheet name="Druskonio perlai VII" sheetId="19" r:id="rId12"/>
+    <sheet name="Birelių namas II" sheetId="18" r:id="rId13"/>
+    <sheet name="Sūduvos 8-2" sheetId="17" r:id="rId14"/>
+    <sheet name="Miškininkų 30 II" sheetId="16" r:id="rId15"/>
+    <sheet name="Pagojo 1 II" sheetId="15" r:id="rId16"/>
+    <sheet name="Vienbutis Minsko 5A" sheetId="14" r:id="rId17"/>
+    <sheet name="Dvibutis Sodybų 12" sheetId="13" r:id="rId18"/>
+    <sheet name="Sfintii Arhangheli 21" sheetId="11" r:id="rId19"/>
+    <sheet name="Girinaičių 7 II" sheetId="10" r:id="rId20"/>
+    <sheet name="Girios 112 II" sheetId="9" r:id="rId21"/>
+    <sheet name="Piliarožių 10 VI" sheetId="8" r:id="rId22"/>
+    <sheet name="Girinaičių 7" sheetId="7" r:id="rId23"/>
+    <sheet name="Kauno 36-232" sheetId="6" r:id="rId24"/>
+    <sheet name="Sodziaus 7A (1)" sheetId="5" r:id="rId25"/>
+    <sheet name="Sodziaus 7A" sheetId="4" r:id="rId26"/>
+    <sheet name="Pušynas VII" sheetId="3" r:id="rId27"/>
+    <sheet name="Užnerio butai III" sheetId="2" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="102">
   <si>
     <t>Paskola</t>
   </si>
@@ -104,9 +105,6 @@
   </si>
   <si>
     <t>LTV max, %</t>
-  </si>
-  <si>
-    <t>Investuota viso</t>
   </si>
   <si>
     <t>Užnerio butai III</t>
@@ -363,6 +361,15 @@
   <si>
     <t>Vėlavo/Anksčiau</t>
   </si>
+  <si>
+    <t>Užnerio butai XV</t>
+  </si>
+  <si>
+    <t>LT-571</t>
+  </si>
+  <si>
+    <t>Investuota, Eur</t>
+  </si>
 </sst>
 </file>
 
@@ -422,12 +429,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -521,7 +534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -594,6 +607,12 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -620,7 +639,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="102">
+  <dxfs count="106">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1365,11 +1412,11 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63180A35-B029-446C-8428-2E9EA9360DFC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E39EAD4-E07A-4257-8CE0-FEE5A53E37D0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1425,7 +1472,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA0BF96-2C5B-4B6E-B63C-C975C26B2C7A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF1A2E9-B58F-4E36-B448-FD6ECF70125D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1481,7 +1528,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D0705A-5DD9-4DA0-8162-F093A90BCD47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA0BF96-2C5B-4B6E-B63C-C975C26B2C7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1537,7 +1584,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139E4DE8-C656-4C9C-831B-83B7F673283D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D0705A-5DD9-4DA0-8162-F093A90BCD47}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1593,6 +1640,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139E4DE8-C656-4C9C-831B-83B7F673283D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7623111-2B0A-45C7-8958-A3A45FB4FC72}"/>
             </a:ext>
           </a:extLst>
@@ -1628,7 +1731,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1684,7 +1787,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1740,7 +1843,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1796,7 +1899,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1852,7 +1955,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1908,7 +2011,63 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63180A35-B029-446C-8428-2E9EA9360DFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1964,63 +2123,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A229A8B-F3F3-4BE1-8727-DC7A2B21128C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2076,7 +2179,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2132,7 +2235,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2188,7 +2291,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2244,7 +2347,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2300,7 +2403,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2377,6 +2480,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A229A8B-F3F3-4BE1-8727-DC7A2B21128C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2F4B5-CAB1-47E1-8A73-CBE8F66DB2EB}"/>
             </a:ext>
           </a:extLst>
@@ -2412,7 +2571,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2468,7 +2627,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2524,7 +2683,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2580,7 +2739,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2636,7 +2795,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2658,62 +2817,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2E05F0-3B0A-43F4-87A0-0AAA040BEF63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF1A2E9-B58F-4E36-B448-FD6ECF70125D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3011,7 +3114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -3025,73 +3128,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="O1" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="O1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="I2" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>0</v>
@@ -3100,16 +3203,16 @@
         <v>5</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>0</v>
@@ -3118,19 +3221,19 @@
         <v>5</v>
       </c>
       <c r="U2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="W2" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -3191,7 +3294,7 @@
       </c>
       <c r="P3" s="4">
         <f>SUM(G3:G200)-S3</f>
-        <v>1179.6499999999996</v>
+        <v>1186.4799999999998</v>
       </c>
       <c r="Q3" s="4">
         <f>Pinigai!H2</f>
@@ -3199,31 +3302,31 @@
       </c>
       <c r="R3" s="4">
         <f>U3-P3</f>
-        <v>5.0700000000003911</v>
+        <v>0</v>
       </c>
       <c r="S3" s="4">
         <f>SUM(L3:L200)</f>
-        <v>1150.6500000000001</v>
+        <v>1254.3300000000002</v>
       </c>
       <c r="T3" s="4">
         <f>SUM(M3:M200)</f>
-        <v>114.72</v>
+        <v>116.47999999999999</v>
       </c>
       <c r="U3" s="4">
         <f>O3+T3+Q3</f>
-        <v>1184.72</v>
+        <v>1186.48</v>
       </c>
       <c r="V3" s="4">
         <f>U3-O3</f>
-        <v>154.72000000000003</v>
+        <v>156.48000000000002</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>0.15021359223300973</v>
+        <v>0.15192233009708739</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12994449734687805</v>
+        <v>0.13074142336845396</v>
       </c>
       <c r="AC3" s="4" t="str">
         <f ca="1">'Užnerio butai III'!AA2</f>
@@ -3724,7 +3827,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Sfintii Arhangheli 21'!B13</f>
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!S3</f>
@@ -3838,7 +3941,7 @@
       </c>
       <c r="J14" s="10">
         <f ca="1">'Vienbutis Minsko 5A'!B13</f>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Vienbutis Minsko 5A'!S3</f>
@@ -3952,7 +4055,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Miškininkų 30 II'!B13</f>
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Miškininkų 30 II'!S3</f>
@@ -4009,7 +4112,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Sūduvos 8-2'!B13</f>
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Sūduvos 8-2'!S3</f>
@@ -4066,7 +4169,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Birelių namas II'!B13</f>
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Birelių namas II'!S3</f>
@@ -4180,7 +4283,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Vingio namai XIV'!B13</f>
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Vingio namai XIV'!S3</f>
@@ -4294,7 +4397,7 @@
       </c>
       <c r="J22" s="10">
         <f ca="1">'Namas Panevėžyje'!B13</f>
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K22" s="10" t="str">
         <f ca="1">'Namas Panevėžyje'!S3</f>
@@ -4345,29 +4448,29 @@
         <f>'Žemoji 52 XXIX“'!B12</f>
         <v>46220</v>
       </c>
-      <c r="I23" s="21" t="str">
+      <c r="I23" s="21">
         <f>'Žemoji 52 XXIX“'!R3</f>
-        <v/>
-      </c>
-      <c r="J23" s="10">
+        <v>46232</v>
+      </c>
+      <c r="J23" s="10" t="str">
         <f ca="1">'Žemoji 52 XXIX“'!B13</f>
-        <v>-10</v>
-      </c>
-      <c r="K23" s="10">
+        <v/>
+      </c>
+      <c r="K23" s="10" t="str">
         <f ca="1">'Žemoji 52 XXIX“'!S3</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="L23" s="4">
         <f>'Žemoji 52 XXIX“'!N3</f>
-        <v>0</v>
+        <v>103.68</v>
       </c>
       <c r="M23" s="4">
         <f>'Žemoji 52 XXIX“'!P3</f>
-        <v>2.76</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="AC23" s="4" t="str">
         <f ca="1">'Žemoji 52 XXIX“'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
@@ -4408,11 +4511,11 @@
       </c>
       <c r="J24" s="10">
         <f ca="1">'Horizonto 2A XII'!B13</f>
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K24" s="10">
         <f ca="1">'Horizonto 2A XII'!S3</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L24" s="4">
         <f>'Horizonto 2A XII'!N3</f>
@@ -4465,7 +4568,7 @@
       </c>
       <c r="J25" s="10">
         <f ca="1">'Tautvilo kotedžai XIV'!B13</f>
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K25" s="10" t="str">
         <f ca="1">'Tautvilo kotedžai XIV'!S3</f>
@@ -4522,7 +4625,7 @@
       </c>
       <c r="J26" s="10">
         <f ca="1">'Kauno 36-118 II'!B13</f>
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K26" s="10" t="str">
         <f ca="1">'Kauno 36-118 II'!S3</f>
@@ -4579,7 +4682,7 @@
       </c>
       <c r="J27" s="10">
         <f ca="1">'Vakaro 3A K1 III'!B13</f>
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K27" s="10" t="str">
         <f ca="1">'Vakaro 3A K1 III'!S3</f>
@@ -4596,6 +4699,63 @@
       <c r="AC27" s="4" t="str">
         <f ca="1">'Vakaro 3A K1 III'!AA2</f>
         <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11">
+        <f>'Užnerio butai XV'!B3</f>
+        <v>46232</v>
+      </c>
+      <c r="C28" s="23" t="str">
+        <f>'Užnerio butai XV'!B2</f>
+        <v>Užnerio butai XV</v>
+      </c>
+      <c r="D28" s="2">
+        <f>'Užnerio butai XV'!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f>'Užnerio butai XV'!B5</f>
+        <v>C</v>
+      </c>
+      <c r="F28" s="14">
+        <f>'Užnerio butai XV'!B10</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="G28" s="4">
+        <f>'Užnerio butai XV'!B11</f>
+        <v>110.51</v>
+      </c>
+      <c r="H28" s="21">
+        <f>'Užnerio butai XV'!B12</f>
+        <v>46597</v>
+      </c>
+      <c r="I28" s="21" t="str">
+        <f>'Užnerio butai XV'!R3</f>
+        <v/>
+      </c>
+      <c r="J28" s="10">
+        <f ca="1">'Užnerio butai XV'!B13</f>
+        <v>365</v>
+      </c>
+      <c r="K28" s="10" t="str">
+        <f ca="1">'Užnerio butai XV'!S3</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>'Užnerio butai XV'!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <f>'Užnerio butai XV'!P3</f>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="4">
+        <f>'Vakaro 3A K1 III'!AA3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4606,11 +4766,11 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:X1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="101" priority="14">
+  <conditionalFormatting sqref="A3:M28">
+    <cfRule type="expression" dxfId="105" priority="14">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="15">
+    <cfRule type="expression" dxfId="104" priority="15">
       <formula>$AC3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4640,6 +4800,7 @@
     <hyperlink ref="C25" location="'Tautvilo kotedžai XIV'!A1" display="'Tautvilo kotedžai XIV'!A1" xr:uid="{82832844-E13C-4822-8606-3FEDED876C80}"/>
     <hyperlink ref="C26" location="'Kauno 36-118 II'!A1" display="'Kauno 36-118 II'!A1" xr:uid="{75F7657E-0901-4A74-80BC-7EA18729A2C1}"/>
     <hyperlink ref="C27" location="'Vakaro 3A K1 III'!A1" display="'Vakaro 3A K1 III'!A1" xr:uid="{89BFE9E6-796F-48DC-A364-A05791FA2A1D}"/>
+    <hyperlink ref="C28" location="'Vakaro 3A K1 III'!A1" display="'Vakaro 3A K1 III'!A1" xr:uid="{4C8CFE6A-8D07-4CE1-93FF-AD4D69ED5247}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4647,6 +4808,935 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46174</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.89</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>2.89</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46174</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="Y2" s="11">
+        <f>B4</f>
+        <v>46057</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>B11*-1</f>
+        <v>-103.62</v>
+      </c>
+      <c r="AA2" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46056</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>B11</f>
+        <v>103.62</v>
+      </c>
+      <c r="N3" s="4">
+        <f>G42</f>
+        <v>103.62</v>
+      </c>
+      <c r="O3" s="4">
+        <f>F42</f>
+        <v>6.6400000000000006</v>
+      </c>
+      <c r="P3" s="4">
+        <f>H42+I42</f>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
+        <v>8.9719572663307198E-2</v>
+      </c>
+      <c r="R3" s="11">
+        <f>IF(M3=N3,B14,"")</f>
+        <v>46211</v>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>46174</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>G2+H2+I2</f>
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46057</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46330</v>
+      </c>
+      <c r="E4" s="4">
+        <v>103.62</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1.57</v>
+      </c>
+      <c r="G4" s="4">
+        <v>103.62</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11">
+        <v>46211</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="0"/>
+        <v>-119</v>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y14" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="2"/>
+        <v>104.53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="4">
+        <v>103.62</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="20">
+        <v>46330</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46211</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="2">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v>-119</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="8"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="8"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="8"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D19" s="8"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="8"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="8"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="8"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="8"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="8"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="8"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="8"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="8"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D41" s="8"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4">
+        <f>SUM(E2:E41)</f>
+        <v>103.62</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>6.6400000000000006</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="3"/>
+        <v>103.62</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="3"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="R1:R2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="75" priority="4">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="5">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="73" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="72" priority="2">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4669,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -4687,39 +5777,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -4727,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="11">
         <v>46174</v>
@@ -4755,20 +5845,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46055</v>
@@ -4881,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46420</v>
@@ -5046,7 +6136,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>123.63</v>
@@ -5073,7 +6163,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46420</v>
@@ -5100,11 +6190,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -5128,7 +6218,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -5153,7 +6243,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -5568,7 +6658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5594,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -5612,39 +6702,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -5652,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="11">
         <v>46142</v>
@@ -5680,20 +6770,20 @@
         <v>-56</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46043</v>
@@ -5822,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46408</v>
@@ -5995,7 +7085,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>118.77</v>
@@ -6022,7 +7112,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46408</v>
@@ -6049,7 +7139,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -6077,7 +7167,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="20">
         <v>46086</v>
@@ -6104,7 +7194,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -6519,7 +7609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6542,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -6560,39 +7650,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -6600,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" s="11">
         <v>46112</v>
@@ -6628,20 +7718,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46013</v>
@@ -6762,7 +7852,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11">
         <v>46378</v>
@@ -6927,7 +8017,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>10</v>
@@ -6954,7 +8044,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46378</v>
@@ -6981,11 +8071,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -7009,7 +8099,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -7034,7 +8124,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -7449,7 +8539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7472,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -7490,39 +8580,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -7530,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="11">
         <v>46112</v>
@@ -7558,20 +8648,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46003</v>
@@ -7692,7 +8782,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46371</v>
@@ -7857,7 +8947,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>106.06</v>
@@ -7884,7 +8974,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46371</v>
@@ -7911,11 +9001,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -7939,7 +9029,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -7964,7 +9054,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -8379,7 +9469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8402,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -8420,39 +9510,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -8460,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="11">
         <v>46083</v>
@@ -8488,20 +9578,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45967</v>
@@ -8622,7 +9712,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13">
         <v>46332</v>
@@ -8787,7 +9877,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>10</v>
@@ -8814,7 +9904,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46332</v>
@@ -8841,11 +9931,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -8869,7 +9959,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -8894,7 +9984,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -9309,7 +10399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9335,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -9353,39 +10443,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -9393,7 +10483,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="11">
         <v>46055</v>
@@ -9421,20 +10511,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45951</v>
@@ -9563,7 +10653,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="4"/>
@@ -9722,7 +10812,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>108.26</v>
@@ -9749,7 +10839,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46224</v>
@@ -9776,7 +10866,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -9804,7 +10894,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="20">
         <v>46072</v>
@@ -9831,7 +10921,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -10246,7 +11336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10269,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -10287,39 +11377,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -10327,7 +11417,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="11">
         <v>46022</v>
@@ -10355,20 +11445,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45916</v>
@@ -10497,7 +11587,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13">
         <v>46281</v>
@@ -10662,7 +11752,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>101.49</v>
@@ -10689,7 +11779,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46281</v>
@@ -10716,11 +11806,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -10744,7 +11834,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -10769,7 +11859,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -11184,7 +12274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -11210,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -11228,39 +12318,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -11268,7 +12358,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="11">
         <v>46022</v>
@@ -11296,20 +12386,20 @@
         <v>19</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45917</v>
@@ -11438,7 +12528,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="4"/>
@@ -11597,7 +12687,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -11624,7 +12714,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46098</v>
@@ -11651,7 +12741,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -11679,7 +12769,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="20">
         <v>46084</v>
@@ -11706,7 +12796,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -12121,7 +13211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12144,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -12162,39 +13252,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -12202,7 +13292,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="11">
         <v>46022</v>
@@ -12230,20 +13320,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45908</v>
@@ -12372,7 +13462,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="13">
         <v>46274</v>
@@ -12537,7 +13627,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>123.24</v>
@@ -12564,7 +13654,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46274</v>
@@ -12591,11 +13681,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -12619,7 +13709,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -12644,7 +13734,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -13059,7 +14149,341 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K200"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="24"/>
+      <c r="F1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>45719</v>
+      </c>
+      <c r="B2" s="4">
+        <v>200</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>SUM(B2:B39)</f>
+        <v>1030</v>
+      </c>
+      <c r="G2" s="4">
+        <f>SUM(C2:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <f>SUM(D2:D39)</f>
+        <v>40</v>
+      </c>
+      <c r="I2" s="4">
+        <f>F2-G2</f>
+        <v>1030</v>
+      </c>
+      <c r="K2">
+        <f>B2*-1</f>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>45725</v>
+      </c>
+      <c r="B3" s="4">
+        <v>100</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K17" si="0">B3*-1</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>45729</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>45743</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>45757</v>
+      </c>
+      <c r="B6" s="4">
+        <v>100</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>45764</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>45770</v>
+      </c>
+      <c r="B8" s="4">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>45791</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>45908</v>
+      </c>
+      <c r="B10" s="4">
+        <v>100</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>45919</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>45957</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46002</v>
+      </c>
+      <c r="B13" s="4">
+        <v>100</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46010</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>46095</v>
+      </c>
+      <c r="B15" s="4">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="12">
+        <f ca="1">TODAY()</f>
+        <v>46232</v>
+      </c>
+      <c r="K200" s="25">
+        <f>Overview!U3</f>
+        <v>1186.48</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -13085,7 +14509,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -13103,39 +14527,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -13143,7 +14567,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="11">
         <v>45901</v>
@@ -13171,20 +14595,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45791</v>
@@ -13299,7 +14723,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -13458,7 +14882,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>100</v>
@@ -13485,7 +14909,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>45975</v>
@@ -13512,7 +14936,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -13540,7 +14964,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>45912</v>
@@ -13567,7 +14991,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -13982,341 +15406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>45719</v>
-      </c>
-      <c r="B2" s="4">
-        <v>200</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <f>SUM(B2:B39)</f>
-        <v>1030</v>
-      </c>
-      <c r="G2" s="4">
-        <f>SUM(C2:C39)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <f>SUM(D2:D39)</f>
-        <v>40</v>
-      </c>
-      <c r="I2" s="4">
-        <f>F2-G2</f>
-        <v>1030</v>
-      </c>
-      <c r="K2">
-        <f>B2*-1</f>
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>45725</v>
-      </c>
-      <c r="B3" s="4">
-        <v>100</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K17" si="0">B3*-1</f>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>45729</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>45743</v>
-      </c>
-      <c r="B5" s="4">
-        <v>100</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>45757</v>
-      </c>
-      <c r="B6" s="4">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>45764</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>45770</v>
-      </c>
-      <c r="B8" s="4">
-        <v>100</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>45791</v>
-      </c>
-      <c r="B9" s="4">
-        <v>100</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>45908</v>
-      </c>
-      <c r="B10" s="4">
-        <v>100</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>45919</v>
-      </c>
-      <c r="B11" s="4">
-        <v>100</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>45957</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>46002</v>
-      </c>
-      <c r="B13" s="4">
-        <v>100</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46010</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>10</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="4">
-        <v>30</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="12">
-        <f ca="1">TODAY()</f>
-        <v>46230</v>
-      </c>
-      <c r="K200" s="25">
-        <f>Overview!U3</f>
-        <v>1184.72</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -14342,7 +15432,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -14360,39 +15450,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -14400,7 +15490,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="11">
         <v>45869</v>
@@ -14428,20 +15518,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45770</v>
@@ -14570,7 +15660,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46140</v>
@@ -14743,7 +15833,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>100</v>
@@ -14770,7 +15860,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46140</v>
@@ -14797,7 +15887,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -14825,7 +15915,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46073</v>
@@ -14852,7 +15942,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -15267,7 +16357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -15293,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -15311,39 +16401,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -15351,7 +16441,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="11">
         <v>45869</v>
@@ -15379,20 +16469,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45764</v>
@@ -15521,7 +16611,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46055</v>
@@ -15708,7 +16798,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>10</v>
@@ -15735,7 +16825,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46136</v>
@@ -15762,7 +16852,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -15790,7 +16880,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46105</v>
@@ -15817,7 +16907,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -16232,7 +17322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -16258,7 +17348,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -16276,39 +17366,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -16316,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="11">
         <v>45869</v>
@@ -16344,20 +17434,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45757</v>
@@ -16472,7 +17562,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -16631,7 +17721,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -16658,7 +17748,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>45948</v>
@@ -16685,7 +17775,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -16713,7 +17803,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>45911</v>
@@ -16740,7 +17830,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -17154,7 +18244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -17180,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -17198,39 +18288,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -17238,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="11">
         <v>45838</v>
@@ -17266,20 +18356,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45743</v>
@@ -17408,7 +18498,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46028</v>
@@ -17595,7 +18685,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -17622,7 +18712,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46112</v>
@@ -17649,7 +18739,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -17677,7 +18767,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46035</v>
@@ -17704,7 +18794,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -18118,7 +19208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -18144,7 +19234,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -18162,39 +19252,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -18202,7 +19292,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="11">
         <v>45838</v>
@@ -18230,20 +19320,20 @@
         <v>16</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45729</v>
@@ -18372,7 +19462,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -18426,7 +19516,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2"/>
@@ -18531,7 +19621,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -18558,7 +19648,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46005</v>
@@ -18585,7 +19675,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -18613,7 +19703,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46049</v>
@@ -18640,7 +19730,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -19270,7 +20360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -19296,7 +20386,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -19314,39 +20404,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -19354,7 +20444,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="11">
         <v>45838</v>
@@ -19382,20 +20472,20 @@
         <v>16</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45725</v>
@@ -19524,7 +20614,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -19578,7 +20668,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2"/>
@@ -19683,7 +20773,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>100</v>
@@ -19710,7 +20800,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46005</v>
@@ -19737,7 +20827,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -19765,7 +20855,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46049</v>
@@ -19792,7 +20882,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -20423,7 +21513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -20449,7 +21539,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -20467,39 +21557,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -20507,7 +21597,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="11">
         <v>45838</v>
@@ -20535,20 +21625,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45721</v>
@@ -20677,7 +21767,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="11">
         <v>46054</v>
@@ -20850,7 +21940,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2">
         <v>100</v>
@@ -20877,7 +21967,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46054</v>
@@ -20904,7 +21994,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -20932,7 +22022,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46056</v>
@@ -20959,7 +22049,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -21592,7 +22682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -21615,10 +22705,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -21636,39 +22726,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -21676,7 +22766,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="11">
         <v>45838</v>
@@ -21704,20 +22794,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45719</v>
@@ -21846,7 +22936,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46087</v>
@@ -22019,7 +23109,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -22046,7 +23136,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46087</v>
@@ -22073,7 +23163,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
@@ -22101,7 +23191,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="11">
         <v>46091</v>
@@ -22128,7 +23218,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -22762,6 +23852,894 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1A0671-14D9-4590-9CB7-560703BB8637}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA1" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="10" t="str">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v/>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="Y2" s="11">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>B11*-1</f>
+        <v>-110.51</v>
+      </c>
+      <c r="AA2" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46232</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>B11</f>
+        <v>110.51</v>
+      </c>
+      <c r="N3" s="4">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <f>F42</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <f>H42+I42</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="11" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>G2+H2+I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y14" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="4">
+        <v>110.51</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="29">
+        <v>46597</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="10">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>365</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="28"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="28"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="28"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D19" s="28"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="28"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="28"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="28"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="28"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="28"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="28"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="28"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="28"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="28"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="28"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="28"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="28"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="28"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="28"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="28"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="28"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="28"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="28"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="28"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="28"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="28"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D41" s="28"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4">
+        <f>SUM(E2:E41)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="103" priority="3">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="101" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="100" priority="2">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D1DFE8-4730-46B9-AA04-8B9A813ABE1E}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22784,7 +24762,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -22802,39 +24780,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -22842,7 +24820,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="11">
         <v>46329</v>
@@ -22862,20 +24840,20 @@
         <v/>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>0</v>
@@ -22986,7 +24964,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46577</v>
@@ -23151,7 +25129,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>142.38999999999999</v>
@@ -23178,7 +25156,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46577</v>
@@ -23205,11 +25183,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -23233,11 +25211,9 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46211</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B14" s="11"/>
       <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -23260,7 +25236,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -23675,7 +25651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23698,7 +25674,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -23716,39 +25692,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -23756,7 +25732,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="11">
         <v>46203</v>
@@ -23784,20 +25760,20 @@
         <v>10</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46097</v>
@@ -23910,7 +25886,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11">
         <v>46462</v>
@@ -24075,7 +26051,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>102.01</v>
@@ -24102,7 +26078,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="11">
         <v>46462</v>
@@ -24129,11 +26105,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -24157,11 +26133,9 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46211</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B14" s="11"/>
       <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -24184,7 +26158,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -24599,7 +26573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24622,7 +26596,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -24640,39 +26614,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -24680,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="11">
         <v>46203</v>
@@ -24708,20 +26682,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46092</v>
@@ -24834,7 +26808,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>46477</v>
@@ -25005,7 +26979,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -25032,7 +27006,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46549</v>
@@ -25059,11 +27033,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -25087,11 +27061,9 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46211</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B14" s="11"/>
       <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -25114,7 +27086,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -25529,7 +27501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25552,7 +27524,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -25570,39 +27542,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -25610,7 +27582,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="11">
         <v>46203</v>
@@ -25630,20 +27602,20 @@
         <v/>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46091</v>
@@ -25707,7 +27679,7 @@
       </c>
       <c r="S3" s="2">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -25756,7 +27728,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -25915,7 +27887,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>100</v>
@@ -25942,7 +27914,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46365</v>
@@ -25969,11 +27941,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -25997,7 +27969,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -26022,7 +27994,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -26437,8 +28409,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26460,7 +28435,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -26478,39 +28453,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -26518,7 +28493,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" s="11">
         <v>46174</v>
@@ -26546,20 +28521,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -26570,7 +28545,7 @@
       </c>
       <c r="AA2" s="2" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -26589,13 +28564,21 @@
       <c r="F3" s="4">
         <v>1.26</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="4">
+        <v>103.68</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.26</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46232</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="M3" s="4">
         <f>B11</f>
@@ -26603,7 +28586,7 @@
       </c>
       <c r="N3" s="4">
         <f>G42</f>
-        <v>0</v>
+        <v>103.68</v>
       </c>
       <c r="O3" s="4">
         <f>F42</f>
@@ -26611,19 +28594,19 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>2.76</v>
-      </c>
-      <c r="Q3" s="14" t="str">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="Q3" s="14">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="11" t="str">
+        <v>0.1039396107196808</v>
+      </c>
+      <c r="R3" s="11">
         <f>IF(M3=N3,B14,"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="2">
+        <v>46232</v>
+      </c>
+      <c r="S3" s="2" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -26654,11 +28637,11 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
+        <v>46232</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
-        <v>0</v>
+        <v>105.44000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -26666,7 +28649,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -26825,7 +28808,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>103.68</v>
@@ -26852,9 +28835,9 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="20">
+        <v>85</v>
+      </c>
+      <c r="B12" s="11">
         <v>46220</v>
       </c>
       <c r="D12" s="11"/>
@@ -26879,11 +28862,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="10">
+        <v>90</v>
+      </c>
+      <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-10</v>
+        <v/>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -26907,9 +28890,11 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="15"/>
+        <v>45</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46232</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -26932,11 +28917,11 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="2" t="str">
+        <v>98</v>
+      </c>
+      <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="4"/>
@@ -27302,15 +29287,15 @@
       </c>
       <c r="G42" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>103.68</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>2.76</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -27347,7 +29332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27370,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>9</v>
@@ -27388,39 +29373,39 @@
         <v>5</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -27428,7 +29413,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" s="11">
         <v>46174</v>
@@ -27456,20 +29441,20 @@
         <v>0</v>
       </c>
       <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -27582,7 +29567,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="4"/>
@@ -27741,7 +29726,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B11" s="4">
         <v>157.15</v>
@@ -27768,7 +29753,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20">
         <v>46346</v>
@@ -27795,11 +29780,11 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -27823,7 +29808,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="15"/>
       <c r="D14" s="8"/>
@@ -27848,7 +29833,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="str">
         <f>IF(M3=N3,B14-B12,"")</f>
@@ -28261,933 +30246,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:AA42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="19" width="10.7109375" customWidth="1"/>
-    <col min="20" max="24" width="8.7109375" customWidth="1"/>
-    <col min="25" max="27" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="11">
-        <v>46174</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>2.89</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>2.89</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11">
-        <v>46174</v>
-      </c>
-      <c r="K2" s="10">
-        <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="Y2" s="11">
-        <f>B4</f>
-        <v>46057</v>
-      </c>
-      <c r="Z2" s="4">
-        <f>B11*-1</f>
-        <v>-103.62</v>
-      </c>
-      <c r="AA2" s="2" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="11">
-        <v>46056</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46265</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
-        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="M3" s="4">
-        <f>B11</f>
-        <v>103.62</v>
-      </c>
-      <c r="N3" s="4">
-        <f>G42</f>
-        <v>103.62</v>
-      </c>
-      <c r="O3" s="4">
-        <f>F42</f>
-        <v>6.6400000000000006</v>
-      </c>
-      <c r="P3" s="4">
-        <f>H42+I42</f>
-        <v>3.8000000000000003</v>
-      </c>
-      <c r="Q3" s="14">
-        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
-        <v>8.9719572663307198E-2</v>
-      </c>
-      <c r="R3" s="11">
-        <f>IF(M3=N3,B14,"")</f>
-        <v>46211</v>
-      </c>
-      <c r="S3" s="2" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="11">
-        <f>J2</f>
-        <v>46174</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>G2+H2+I2</f>
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="11">
-        <v>46057</v>
-      </c>
-      <c r="D4" s="11">
-        <v>46330</v>
-      </c>
-      <c r="E4" s="4">
-        <v>103.62</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1.57</v>
-      </c>
-      <c r="G4" s="4">
-        <v>103.62</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0.91</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11">
-        <v>46211</v>
-      </c>
-      <c r="K4" s="10">
-        <f t="shared" si="0"/>
-        <v>-119</v>
-      </c>
-      <c r="Y4" s="11">
-        <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y5" s="11">
-        <f t="shared" si="1"/>
-        <v>46211</v>
-      </c>
-      <c r="Z5" s="4">
-        <f t="shared" si="2"/>
-        <v>104.53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y6" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.65</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y7" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2">
-        <v>9</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y8" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y9" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4">
-        <v>103.62</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y11" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="20">
-        <v>46330</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y12" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="10" t="str">
-        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y13" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46211</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y14" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="2">
-        <f>IF(M3=N3,B14-B12,"")</f>
-        <v>-119</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="8"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" s="8"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="8"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" s="8"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20" s="8"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21" s="8"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="8"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="8"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="8"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="8"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="8"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D27" s="8"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D28" s="8"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D29" s="8"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="8"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D31" s="8"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="8"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="8"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="8"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D35" s="8"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D36" s="8"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D37" s="8"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="8"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="8"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D40" s="8"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D41" s="8"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D42" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="4">
-        <f>SUM(E2:E41)</f>
-        <v>103.62</v>
-      </c>
-      <c r="F42" s="4">
-        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>6.6400000000000006</v>
-      </c>
-      <c r="G42" s="4">
-        <f t="shared" si="3"/>
-        <v>103.62</v>
-      </c>
-      <c r="H42" s="4">
-        <f t="shared" si="3"/>
-        <v>3.8000000000000003</v>
-      </c>
-      <c r="I42" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="R1:R2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="75" priority="4">
-      <formula>$M$3=$N$3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="5">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="73" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="72" priority="2">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/excel/Crowdpear.xlsx
+++ b/excel/Crowdpear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-v2\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Crowdpear\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34883093-1794-4D37-985D-5F9AA8E5449C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5D66E7-71A4-426B-A863-4C7DDD7F5D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="19" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -429,18 +429,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -534,7 +528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -607,12 +601,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,6 +621,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3128,39 +3119,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="O1" s="33" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="O1" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="34" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34" t="s">
+      <c r="T1" s="32"/>
+      <c r="U1" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -3326,7 +3317,7 @@
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.13074142336845396</v>
+        <v>0.12784344553947447</v>
       </c>
       <c r="AC3" s="4" t="str">
         <f ca="1">'Užnerio butai III'!AA2</f>
@@ -3827,7 +3818,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Sfintii Arhangheli 21'!B13</f>
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!S3</f>
@@ -3941,7 +3932,7 @@
       </c>
       <c r="J14" s="10">
         <f ca="1">'Vienbutis Minsko 5A'!B13</f>
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Vienbutis Minsko 5A'!S3</f>
@@ -4055,7 +4046,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Miškininkų 30 II'!B13</f>
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Miškininkų 30 II'!S3</f>
@@ -4112,7 +4103,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Sūduvos 8-2'!B13</f>
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Sūduvos 8-2'!S3</f>
@@ -4169,7 +4160,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Birelių namas II'!B13</f>
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Birelių namas II'!S3</f>
@@ -4283,7 +4274,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Vingio namai XIV'!B13</f>
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Vingio namai XIV'!S3</f>
@@ -4397,7 +4388,7 @@
       </c>
       <c r="J22" s="10">
         <f ca="1">'Namas Panevėžyje'!B13</f>
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K22" s="10" t="str">
         <f ca="1">'Namas Panevėžyje'!S3</f>
@@ -4511,11 +4502,11 @@
       </c>
       <c r="J24" s="10">
         <f ca="1">'Horizonto 2A XII'!B13</f>
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="K24" s="10">
         <f ca="1">'Horizonto 2A XII'!S3</f>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L24" s="4">
         <f>'Horizonto 2A XII'!N3</f>
@@ -4568,7 +4559,7 @@
       </c>
       <c r="J25" s="10">
         <f ca="1">'Tautvilo kotedžai XIV'!B13</f>
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="K25" s="10" t="str">
         <f ca="1">'Tautvilo kotedžai XIV'!S3</f>
@@ -4625,7 +4616,7 @@
       </c>
       <c r="J26" s="10">
         <f ca="1">'Kauno 36-118 II'!B13</f>
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="K26" s="10" t="str">
         <f ca="1">'Kauno 36-118 II'!S3</f>
@@ -4682,7 +4673,7 @@
       </c>
       <c r="J27" s="10">
         <f ca="1">'Vakaro 3A K1 III'!B13</f>
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="K27" s="10" t="str">
         <f ca="1">'Vakaro 3A K1 III'!S3</f>
@@ -4731,7 +4722,7 @@
       </c>
       <c r="H28" s="21">
         <f>'Užnerio butai XV'!B12</f>
-        <v>46597</v>
+        <v>46603</v>
       </c>
       <c r="I28" s="21" t="str">
         <f>'Užnerio butai XV'!R3</f>
@@ -4739,7 +4730,7 @@
       </c>
       <c r="J28" s="10">
         <f ca="1">'Užnerio butai XV'!B13</f>
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K28" s="10" t="str">
         <f ca="1">'Užnerio butai XV'!S3</f>
@@ -4859,21 +4850,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -4930,9 +4921,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46057</v>
@@ -5785,21 +5776,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -5856,9 +5847,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46055</v>
@@ -6194,7 +6185,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -6710,21 +6701,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -6781,9 +6772,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46043</v>
@@ -7658,21 +7649,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -7729,9 +7720,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46013</v>
@@ -8075,7 +8066,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -8588,21 +8579,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -8659,9 +8650,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46003</v>
@@ -9005,7 +8996,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -9518,21 +9509,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -9589,9 +9580,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45967</v>
@@ -9935,7 +9926,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -10451,21 +10442,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -10522,9 +10513,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45951</v>
@@ -11385,21 +11376,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -11456,9 +11447,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45916</v>
@@ -11810,7 +11801,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -12326,21 +12317,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -12397,9 +12388,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45917</v>
@@ -13260,21 +13251,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -13331,9 +13322,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45908</v>
@@ -13685,7 +13676,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -14469,7 +14460,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
+        <v>46241</v>
       </c>
       <c r="K200" s="25">
         <f>Overview!U3</f>
@@ -14535,21 +14526,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -14606,9 +14597,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45791</v>
@@ -15458,21 +15449,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -15529,9 +15520,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45770</v>
@@ -16409,21 +16400,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -16480,9 +16471,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45764</v>
@@ -17374,21 +17365,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -17445,9 +17436,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45757</v>
@@ -18296,21 +18287,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -18367,9 +18358,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45743</v>
@@ -19260,21 +19251,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -19331,9 +19322,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45729</v>
@@ -20412,21 +20403,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -20483,9 +20474,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45725</v>
@@ -21565,21 +21556,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -21636,9 +21627,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45721</v>
@@ -22734,21 +22725,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -22805,9 +22796,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45719</v>
@@ -23876,22 +23867,22 @@
       <c r="B1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="28" t="s">
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28" t="s">
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J1" s="9" t="s">
@@ -23900,30 +23891,30 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="28" t="s">
+      <c r="AA1" s="8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -23934,9 +23925,15 @@
       <c r="B2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="D2" s="11">
+        <v>46329</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.74</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -23951,18 +23948,18 @@
       <c r="N2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
-        <v>0</v>
+        <v>46238</v>
       </c>
       <c r="Z2" s="4">
         <f>B11*-1</f>
@@ -23980,9 +23977,15 @@
       <c r="B3" s="11">
         <v>46232</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="D3" s="11">
+        <v>46419</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.57</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -24001,7 +24004,7 @@
       </c>
       <c r="O3" s="4">
         <f>F42</f>
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
@@ -24032,10 +24035,18 @@
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="11">
+        <v>46238</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46507</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.6</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -24060,9 +24071,15 @@
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="D5" s="11">
+        <v>46603</v>
+      </c>
+      <c r="E5" s="4">
+        <v>110.51</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.74</v>
+      </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -24115,7 +24132,7 @@
         <v>0.75</v>
       </c>
       <c r="D7" s="11"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2"/>
       <c r="H7" s="4"/>
@@ -24142,7 +24159,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="11"/>
-      <c r="E8" s="15"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
@@ -24169,7 +24186,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="15"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
@@ -24196,7 +24213,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="15"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
@@ -24223,7 +24240,7 @@
         <v>110.51</v>
       </c>
       <c r="D11" s="11"/>
-      <c r="E11" s="15"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -24246,11 +24263,11 @@
       <c r="A12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="29">
-        <v>46597</v>
+      <c r="B12" s="35">
+        <v>46603</v>
       </c>
       <c r="D12" s="11"/>
-      <c r="E12" s="15"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
@@ -24275,10 +24292,10 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D13" s="11"/>
-      <c r="E13" s="15"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
@@ -24302,7 +24319,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="11"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -24330,7 +24347,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="28"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -24343,7 +24360,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="28"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -24356,7 +24373,7 @@
       </c>
     </row>
     <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" s="28"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -24369,7 +24386,7 @@
       </c>
     </row>
     <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="28"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -24382,7 +24399,7 @@
       </c>
     </row>
     <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" s="28"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -24395,7 +24412,7 @@
       </c>
     </row>
     <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20" s="28"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -24408,7 +24425,7 @@
       </c>
     </row>
     <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21" s="28"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -24421,7 +24438,7 @@
       </c>
     </row>
     <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="28"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -24434,7 +24451,7 @@
       </c>
     </row>
     <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="28"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -24447,7 +24464,7 @@
       </c>
     </row>
     <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="28"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -24460,7 +24477,7 @@
       </c>
     </row>
     <row r="25" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="28"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -24473,7 +24490,7 @@
       </c>
     </row>
     <row r="26" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="28"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -24486,7 +24503,7 @@
       </c>
     </row>
     <row r="27" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D27" s="28"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -24499,7 +24516,7 @@
       </c>
     </row>
     <row r="28" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D28" s="28"/>
+      <c r="D28" s="8"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -24512,7 +24529,7 @@
       </c>
     </row>
     <row r="29" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D29" s="28"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -24525,7 +24542,7 @@
       </c>
     </row>
     <row r="30" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="28"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -24538,7 +24555,7 @@
       </c>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D31" s="28"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -24551,7 +24568,7 @@
       </c>
     </row>
     <row r="32" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="28"/>
+      <c r="D32" s="8"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -24564,7 +24581,7 @@
       </c>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="28"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -24577,7 +24594,7 @@
       </c>
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="28"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -24590,7 +24607,7 @@
       </c>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D35" s="28"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -24603,7 +24620,7 @@
       </c>
     </row>
     <row r="36" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D36" s="28"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -24616,7 +24633,7 @@
       </c>
     </row>
     <row r="37" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D37" s="28"/>
+      <c r="D37" s="8"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -24629,7 +24646,7 @@
       </c>
     </row>
     <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="28"/>
+      <c r="D38" s="8"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -24642,7 +24659,7 @@
       </c>
     </row>
     <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="28"/>
+      <c r="D39" s="8"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -24655,7 +24672,7 @@
       </c>
     </row>
     <row r="40" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D40" s="28"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -24668,7 +24685,7 @@
       </c>
     </row>
     <row r="41" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D41" s="28"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -24681,16 +24698,16 @@
       </c>
     </row>
     <row r="42" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="4">
         <f>SUM(E2:E41)</f>
-        <v>0</v>
+        <v>110.51</v>
       </c>
       <c r="F42" s="4">
         <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>0</v>
+        <v>10.65</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="3"/>
@@ -24788,21 +24805,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -24851,12 +24868,12 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
-        <v>0</v>
+        <v>46212</v>
       </c>
       <c r="Z2" s="4">
         <f>B11*-1</f>
@@ -24932,7 +24949,9 @@
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="11">
+        <v>46212</v>
+      </c>
       <c r="D4" s="11">
         <v>46507</v>
       </c>
@@ -25187,7 +25206,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -25700,21 +25719,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -25771,9 +25790,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46097</v>
@@ -26109,7 +26128,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -26622,21 +26641,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -26693,9 +26712,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46092</v>
@@ -27037,7 +27056,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -27550,21 +27569,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -27613,9 +27632,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46091</v>
@@ -27679,7 +27698,7 @@
       </c>
       <c r="S3" s="2">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -27945,7 +27964,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -28461,21 +28480,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -28532,9 +28551,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -29381,21 +29400,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="30" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -29452,9 +29471,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -29784,7 +29803,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>

--- a/excel/Crowdpear.xlsx
+++ b/excel/Crowdpear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Crowdpear\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Crowdpear\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5D66E7-71A4-426B-A863-4C7DDD7F5D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EEFEA5-F194-4BD4-A1B9-42C74159CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -601,6 +601,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -621,9 +624,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3119,39 +3119,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31" t="s">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="O1" s="31" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="O1" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="32" t="s">
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32" t="s">
+      <c r="T1" s="33"/>
+      <c r="U1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R3" s="4">
         <f>U3-P3</f>
-        <v>0</v>
+        <v>0.22000000000025466</v>
       </c>
       <c r="S3" s="4">
         <f>SUM(L3:L200)</f>
@@ -3301,23 +3301,23 @@
       </c>
       <c r="T3" s="4">
         <f>SUM(M3:M200)</f>
-        <v>116.47999999999999</v>
+        <v>116.69999999999999</v>
       </c>
       <c r="U3" s="4">
         <f>O3+T3+Q3</f>
-        <v>1186.48</v>
+        <v>1186.7</v>
       </c>
       <c r="V3" s="4">
         <f>U3-O3</f>
-        <v>156.48000000000002</v>
+        <v>156.70000000000005</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>0.15192233009708739</v>
+        <v>0.15213592233009712</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12784344553947447</v>
+        <v>0.12087267041206359</v>
       </c>
       <c r="AC3" s="4" t="str">
         <f ca="1">'Užnerio butai III'!AA2</f>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Sfintii Arhangheli 21'!B13</f>
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!S3</f>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="J14" s="10">
         <f ca="1">'Vienbutis Minsko 5A'!B13</f>
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Vienbutis Minsko 5A'!S3</f>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Miškininkų 30 II'!B13</f>
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Miškininkų 30 II'!S3</f>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="M16" s="4">
         <f>'Miškininkų 30 II'!P3</f>
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="AC16" s="4" t="str">
         <f ca="1">'Miškininkų 30 II'!AA2</f>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Sūduvos 8-2'!B13</f>
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Sūduvos 8-2'!S3</f>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Birelių namas II'!B13</f>
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Birelių namas II'!S3</f>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Vingio namai XIV'!B13</f>
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Vingio namai XIV'!S3</f>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="J22" s="10">
         <f ca="1">'Namas Panevėžyje'!B13</f>
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="K22" s="10" t="str">
         <f ca="1">'Namas Panevėžyje'!S3</f>
@@ -4502,11 +4502,11 @@
       </c>
       <c r="J24" s="10">
         <f ca="1">'Horizonto 2A XII'!B13</f>
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="K24" s="10">
         <f ca="1">'Horizonto 2A XII'!S3</f>
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="L24" s="4">
         <f>'Horizonto 2A XII'!N3</f>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="J25" s="10">
         <f ca="1">'Tautvilo kotedžai XIV'!B13</f>
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="K25" s="10" t="str">
         <f ca="1">'Tautvilo kotedžai XIV'!S3</f>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="J26" s="10">
         <f ca="1">'Kauno 36-118 II'!B13</f>
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="K26" s="10" t="str">
         <f ca="1">'Kauno 36-118 II'!S3</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="J27" s="10">
         <f ca="1">'Vakaro 3A K1 III'!B13</f>
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="K27" s="10" t="str">
         <f ca="1">'Vakaro 3A K1 III'!S3</f>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="J28" s="10">
         <f ca="1">'Užnerio butai XV'!B13</f>
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="K28" s="10" t="str">
         <f ca="1">'Užnerio butai XV'!S3</f>
@@ -4850,21 +4850,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -4921,9 +4921,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46057</v>
@@ -5776,21 +5776,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -5847,9 +5847,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46055</v>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -6701,21 +6701,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -6772,9 +6772,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46043</v>
@@ -7649,21 +7649,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -7720,9 +7720,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46013</v>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -8579,21 +8579,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -8650,9 +8650,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46003</v>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -9509,21 +9509,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -9580,9 +9580,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45967</v>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
@@ -9681,13 +9681,21 @@
       <c r="F4" s="4">
         <v>0.22</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11">
+        <v>46265</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
@@ -9724,11 +9732,11 @@
       </c>
       <c r="Y5" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -9926,7 +9934,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -10349,7 +10357,7 @@
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
@@ -10442,21 +10450,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -10513,9 +10521,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45951</v>
@@ -11376,21 +11384,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -11447,9 +11455,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45916</v>
@@ -11801,7 +11809,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -12317,21 +12325,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -12388,9 +12396,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45917</v>
@@ -13251,21 +13259,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -13322,9 +13330,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45908</v>
@@ -13676,7 +13684,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -14460,11 +14468,11 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="K200" s="25">
         <f>Overview!U3</f>
-        <v>1186.48</v>
+        <v>1186.7</v>
       </c>
     </row>
   </sheetData>
@@ -14526,21 +14534,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -14597,9 +14605,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45791</v>
@@ -15449,21 +15457,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -15520,9 +15528,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45770</v>
@@ -16400,21 +16408,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -16471,9 +16479,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45764</v>
@@ -17365,21 +17373,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -17436,9 +17444,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45757</v>
@@ -18287,21 +18295,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -18358,9 +18366,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45743</v>
@@ -19251,21 +19259,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -19322,9 +19330,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45729</v>
@@ -20403,21 +20411,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -20474,9 +20482,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45725</v>
@@ -21556,21 +21564,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -21627,9 +21635,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45721</v>
@@ -22725,21 +22733,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -22796,9 +22804,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45719</v>
@@ -23891,21 +23899,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -23954,9 +23962,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46238</v>
@@ -24263,7 +24271,7 @@
       <c r="A12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="28">
         <v>46603</v>
       </c>
       <c r="D12" s="11"/>
@@ -24292,7 +24300,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="4"/>
@@ -24805,21 +24813,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -24868,9 +24876,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46212</v>
@@ -25206,7 +25214,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -25719,21 +25727,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -25790,9 +25798,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46097</v>
@@ -26128,7 +26136,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -26641,21 +26649,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -26712,9 +26720,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46092</v>
@@ -27056,7 +27064,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -27569,21 +27577,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -27632,9 +27640,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46091</v>
@@ -27698,7 +27706,7 @@
       </c>
       <c r="S3" s="2">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -27964,7 +27972,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -28480,21 +28488,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -28551,9 +28559,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -29400,21 +29408,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
+      <c r="M1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="31"/>
+      <c r="O1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="S1" s="34" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -29471,9 +29479,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -29803,7 +29811,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
